--- a/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:32:36+00:00</t>
+    <t>2025-02-24T13:36:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:36:50+00:00</t>
+    <t>2025-03-04T16:07:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T16:07:16+00:00</t>
+    <t>2025-03-06T10:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T10:23:19+00:00</t>
+    <t>2025-03-10T13:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T13:00:25+00:00</t>
+    <t>2025-03-11T15:29:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T15:29:00+00:00</t>
+    <t>2025-03-12T13:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T13:18:22+00:00</t>
+    <t>2025-03-14T15:47:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-14T15:47:10+00:00</t>
+    <t>2025-03-25T13:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T13:52:25+00:00</t>
+    <t>2025-03-25T14:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T14:07:20+00:00</t>
+    <t>2025-03-31T09:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T09:17:15+00:00</t>
+    <t>2025-04-14T15:21:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Auteur du document (humain ou système)</t>
+    <t>Modèle métier - Auteur du document (humain ou système)</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-14T15:21:44+00:00</t>
+    <t>2025-04-23T09:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -235,7 +235,7 @@
     <t/>
   </si>
   <si>
-    <t>0</t>
+    <t>1</t>
   </si>
   <si>
     <t>*</t>
@@ -248,10 +248,10 @@
     <t>Base</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>Auteur.roleFonctionnel</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
@@ -275,7 +275,7 @@
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/PersonneStructureAuteur
-https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Systeme</t>
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/SystemeStructureAuteur</t>
   </si>
   <si>
     <t>Auteur du document : ce peut être un professionnel, un patient/usager ou un système. Pour un professionnel ou un système, la structure de rattachement doit être précisée.</t>
@@ -583,40 +583,40 @@
   <dimension ref="A1:AJ5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="29.9140625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="29.9140625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="25.64453125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="25.64453125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="86.80078125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="74.4140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.6640625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="19.625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="29.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="25.64453125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
   </cols>
   <sheetData>
@@ -818,7 +818,7 @@
         <v>76</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AH2" t="s" s="2">
         <v>74</v>
@@ -832,10 +832,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -843,10 +843,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G3" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="G3" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>72</v>
@@ -915,13 +915,13 @@
         <v>72</v>
       </c>
       <c r="AF3" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG3" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="AG3" t="s" s="2">
+      <c r="AH3" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="AH3" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>72</v>
@@ -943,10 +943,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>72</v>
@@ -1018,10 +1018,10 @@
         <v>81</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>72</v>
@@ -1043,10 +1043,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>72</v>
@@ -1118,10 +1118,10 @@
         <v>84</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>72</v>

--- a/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:31:53+00:00</t>
+    <t>2025-04-24T14:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T14:52:25+00:00</t>
+    <t>2025-04-28T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:47:42+00:00</t>
+    <t>2025-04-28T07:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:48:19+00:00</t>
+    <t>2025-04-28T09:06:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:06:14+00:00</t>
+    <t>2025-04-28T09:53:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:53:39+00:00</t>
+    <t>2025-05-06T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:44:46+00:00</t>
+    <t>2025-05-06T15:53:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:53:54+00:00</t>
+    <t>2025-05-06T15:58:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:58:22+00:00</t>
+    <t>2025-05-20T10:20:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Auteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T10:20:09+00:00</t>
+    <t>2025-05-20T12:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
